--- a/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed0val/score_seed0val.xlsx
+++ b/ToxCast_model/experiments/prediction/DART_MTL_251228/DART_MTL_seed0val/score_seed0val.xlsx
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.6654440154440154</v>
+        <v>0.6655083655083655</v>
       </c>
       <c r="E171" t="n">
         <v>0.8443579766536965</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.7631801582796987</v>
+        <v>0.7631801582796988</v>
       </c>
       <c r="E188" t="n">
         <v>0.8203517587939698</v>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.7305762104591522</v>
+        <v>0.7305823455790326</v>
       </c>
       <c r="E190" t="n">
         <v>0.8025034770514604</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.9787170263788969</v>
+        <v>0.9787170263788968</v>
       </c>
       <c r="E241" t="n">
         <v>0.9735744089012517</v>
